--- a/restaurant_manager_forms/005_stripe_online_food_order_form--restaurant_manager_forms.xlsx
+++ b/restaurant_manager_forms/005_stripe_online_food_order_form--restaurant_manager_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'restaurant_manager_forms',_'selected':_false}</t>
+          <t>restaurant_manager_forms</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Restaurant Manager Forms', 'selected': False}</t>
+          <t>Restaurant Manager Forms</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other',_'selected':_false}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other', 'selected': False}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'default',_'selected':_true}</t>
+          <t>default</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Default', 'selected': True}</t>
+          <t>Default</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'public_key',_'selected':_false}</t>
+          <t>public_key</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Public Key', 'selected': False}</t>
+          <t>Public Key</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'secret_key',_'selected':_false}</t>
+          <t>secret_key</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Secret Key', 'selected': False}</t>
+          <t>Secret Key</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'none',_'selected':_true}</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'None', 'selected': True}</t>
+          <t>None</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'connect',_'selected':_false}</t>
+          <t>connect</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Connect', 'selected': False}</t>
+          <t>Connect</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'disconnect',_'selected':_false}</t>
+          <t>disconnect</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Disconnect', 'selected': False}</t>
+          <t>Disconnect</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'not_connected',_'selected':_true}</t>
+          <t>not_connected</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Not Connected', 'selected': True}</t>
+          <t>Not Connected</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'restaurant_manager_forms',_'selected':_false}</t>
+          <t>restaurant_manager_forms</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Restaurant Manager Forms', 'selected': False}</t>
+          <t>Restaurant Manager Forms</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'other',_'selected':_false}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Other', 'selected': False}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'default',_'selected':_false}</t>
+          <t>default</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Default', 'selected': False}</t>
+          <t>Default</t>
         </is>
       </c>
     </row>
